--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8</f>
+              <f>'30日跟踪'!$A$8:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8</f>
+              <f>'30日跟踪'!$D$8:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -708,6 +708,26 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>第1/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>160.5599975585938</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1.28051396891955</v>
+      </c>
+      <c r="D9" s="6">
+        <f>B9/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>第2/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$9</f>
+              <f>'30日跟踪'!$A$8:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$9</f>
+              <f>'30日跟踪'!$D$8:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -728,6 +728,26 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>第2/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>163.7200012207031</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1.968113920128944</v>
+      </c>
+      <c r="D10" s="6">
+        <f>B10/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>第3/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$10</f>
+              <f>'30日跟踪'!$A$8:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$10</f>
+              <f>'30日跟踪'!$D$8:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -748,6 +748,26 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>第3/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>164.7799987792969</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.6474453644578437</v>
+      </c>
+      <c r="D11" s="6">
+        <f>B11/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>第4/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$11</f>
+              <f>'30日跟踪'!$A$8:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$11</f>
+              <f>'30日跟踪'!$D$8:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -768,6 +768,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>第4/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>164.1900024414062</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-0.3580509420204936</v>
+      </c>
+      <c r="D12" s="6">
+        <f>B12/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>第5/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$12</f>
+              <f>'30日跟踪'!$A$8:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$12</f>
+              <f>'30日跟踪'!$D$8:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -788,6 +788,26 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>第5/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>170.4799957275391</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3.830923437849076</v>
+      </c>
+      <c r="D13" s="6">
+        <f>B13/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>第6/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="6">
@@ -773,13 +773,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>164.1900024414062</v>
+        <v>170.4799957275391</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3580509420204936</v>
+        <v>3.459155838371286</v>
       </c>
       <c r="D12" s="6">
         <f>B12/$B$8-1</f>
@@ -793,13 +793,13 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>170.4799957275391</v>
+        <v>166.6100006103516</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.830923437849076</v>
+        <v>-2.270058196958502</v>
       </c>
       <c r="D13" s="6">
         <f>B13/$B$8-1</f>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$13</f>
+              <f>'30日跟踪'!$A$8:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$13</f>
+              <f>'30日跟踪'!$D$8:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -773,13 +773,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>170.4799957275391</v>
+        <v>164.1900024414062</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.459155838371286</v>
+        <v>-0.3580509420204936</v>
       </c>
       <c r="D12" s="6">
         <f>B12/$B$8-1</f>
@@ -793,13 +793,13 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>166.6100006103516</v>
+        <v>170.4799957275391</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.270058196958502</v>
+        <v>3.830923437849076</v>
       </c>
       <c r="D13" s="6">
         <f>B13/$B$8-1</f>
@@ -808,6 +808,46 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>第6/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>166.6100006103516</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-2.270058196958502</v>
+      </c>
+      <c r="D14" s="6">
+        <f>B14/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第7/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>169.9600067138672</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2.010687288424085</v>
+      </c>
+      <c r="D15" s="6">
+        <f>B15/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>第8/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$15</f>
+              <f>'30日跟踪'!$A$8:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$15</f>
+              <f>'30日跟踪'!$D$8:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -848,6 +848,46 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>第8/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>168.5700073242188</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-0.8178391002234719</v>
+      </c>
+      <c r="D16" s="6">
+        <f>B16/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>第9/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>168.7400054931641</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0.1008472216640133</v>
+      </c>
+      <c r="D17" s="6">
+        <f>B17/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>第10/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$17</f>
+              <f>'30日跟踪'!$A$8:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$17</f>
+              <f>'30日跟踪'!$D$8:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -888,6 +888,26 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>第10/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>174.0899963378906</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>3.170552726421061</v>
+      </c>
+      <c r="D18" s="6">
+        <f>B18/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>第11/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
+++ b/data/BOLL/EXCLE/QCOM_1_20260824.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$18</f>
+              <f>'30日跟踪'!$A$8:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$18</f>
+              <f>'30日跟踪'!$D$8:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -908,6 +908,26 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>第11/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>176.3999938964844</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1.326898504903351</v>
+      </c>
+      <c r="D19" s="6">
+        <f>B19/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>第12/30个交易日</t>
         </is>
       </c>
     </row>
